--- a/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 32,62</t>
+          <t>-9,01; 30,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 40,31</t>
+          <t>-10,6; 38,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 19,05</t>
+          <t>-25,53; 19,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 67,14</t>
+          <t>-12,07; 58,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 128,2</t>
+          <t>-18,4; 131,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 34,41</t>
+          <t>-31,75; 35,39</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 22,66</t>
+          <t>-12,05; 24,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 10,46</t>
+          <t>-24,02; 9,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 14,42</t>
+          <t>-26,94; 12,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 51,81</t>
+          <t>-18,78; 53,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 18,4</t>
+          <t>-33,09; 17,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 27,48</t>
+          <t>-43,54; 24,21</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 11,97</t>
+          <t>-23,05; 11,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 40,65</t>
+          <t>1,75; 41,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 38,13</t>
+          <t>-29,23; 37,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 19,91</t>
+          <t>-30,49; 18,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 109,67</t>
+          <t>3,79; 113,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 99,81</t>
+          <t>-49,67; 100,39</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 25,01</t>
+          <t>-8,32; 24,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 22,51</t>
+          <t>-19,39; 23,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 25,6</t>
+          <t>-13,15; 26,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 46,65</t>
+          <t>-11,34; 49,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 50,17</t>
+          <t>-29,2; 51,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 53,8</t>
+          <t>-17,33; 53,01</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 14,36</t>
+          <t>-3,93; 12,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 17,0</t>
+          <t>-4,45; 15,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 18,19</t>
+          <t>-12,3; 18,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 25,25</t>
+          <t>-6,04; 22,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 33,29</t>
+          <t>-7,43; 30,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 34,17</t>
+          <t>-20,25; 33,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 30,1</t>
+          <t>-5,33; 30,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 38,17</t>
+          <t>-10,62; 39,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 19,72</t>
+          <t>-26,34; 16,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 58,32</t>
+          <t>-6,74; 64,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 131,87</t>
+          <t>-19,42; 136,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 35,39</t>
+          <t>-32,79; 30,2</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 24,13</t>
+          <t>-12,73; 21,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 9,89</t>
+          <t>-21,47; 11,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 12,61</t>
+          <t>-27,32; 12,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 53,39</t>
+          <t>-20,19; 44,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 17,92</t>
+          <t>-30,57; 21,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 24,21</t>
+          <t>-45,06; 24,73</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 11,58</t>
+          <t>-24,97; 12,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 41,44</t>
+          <t>2,56; 42,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 37,1</t>
+          <t>-28,02; 41,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 18,6</t>
+          <t>-32,22; 19,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 113,51</t>
+          <t>3,99; 120,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,67; 100,39</t>
+          <t>-48,38; 112,45</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 24,86</t>
+          <t>-7,97; 27,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 23,58</t>
+          <t>-18,22; 21,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 26,35</t>
+          <t>-11,88; 27,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 49,23</t>
+          <t>-11,28; 52,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 51,48</t>
+          <t>-27,57; 49,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 53,01</t>
+          <t>-16,3; 60,34</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 12,75</t>
+          <t>-4,01; 14,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,19</t>
+          <t>-3,74; 16,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 18,16</t>
+          <t>-12,88; 17,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 22,05</t>
+          <t>-5,81; 24,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 30,38</t>
+          <t>-6,11; 33,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 33,75</t>
+          <t>-21,41; 34,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,97</t>
+          <t>-5,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,7%</t>
+          <t>-7,93%</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 30,58</t>
+          <t>-6,12; 32,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 39,14</t>
+          <t>-9,6; 40,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 16,44</t>
+          <t>-27,23; 17,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 64,56</t>
+          <t>-8,14; 67,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 136,09</t>
+          <t>-18,1; 128,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 30,2</t>
+          <t>-32,8; 30,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,48</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,64%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 21,06</t>
+          <t>-14,99; 22,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 11,79</t>
+          <t>-22,72; 10,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 12,97</t>
+          <t>-15,51; 18,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 44,4</t>
+          <t>-22,58; 51,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 21,65</t>
+          <t>-31,92; 18,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,06; 24,73</t>
+          <t>-23,78; 38,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>-16,98</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>-30,57%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 12,05</t>
+          <t>-24,72; 11,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 42,28</t>
+          <t>4,3; 40,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 41,03</t>
+          <t>-35,49; 5,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 19,49</t>
+          <t>-31,77; 19,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 120,51</t>
+          <t>6,88; 109,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 112,45</t>
+          <t>-55,86; 10,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 27,44</t>
+          <t>-7,95; 25,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 21,85</t>
+          <t>-19,41; 22,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 27,23</t>
+          <t>-14,87; 26,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 52,53</t>
+          <t>-12,76; 46,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 49,42</t>
+          <t>-29,14; 50,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 60,34</t>
+          <t>-21,62; 57,53</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-4,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,85%</t>
+          <t>-8,36%</t>
         </is>
       </c>
     </row>
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 14,34</t>
+          <t>-4,42; 14,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 16,58</t>
+          <t>-3,41; 17,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 17,95</t>
+          <t>-15,53; 5,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 24,75</t>
+          <t>-6,48; 25,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 33,29</t>
+          <t>-5,76; 33,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 34,33</t>
+          <t>-23,62; 9,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A01-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-7,93%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.925116515843434</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.920469416839319</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.608071122189586</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.3237788268255964</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2629308974177494</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2096088330469567</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.5049659253077935</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.02299794109889645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,12; 32,62</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,6; 40,31</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-27,23; 17,68</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,14; 67,14</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-18,1; 128,2</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-32,8; 30,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.11509322449712</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.185194830728597</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.262811638807612</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.965530480662715</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1429324761702688</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.244537674781306</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2917245252621675</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4013565478538733</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.17371345460818</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.38153682599149</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.23939993837501</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.917093826930001</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.7875698467206291</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.936262077386698</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.860671482049794</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.8068860593582218</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,39</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-9,92%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-14,99; 22,66</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-22,72; 10,46</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-15,51; 18,83</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-22,58; 51,81</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-31,92; 18,4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-23,78; 38,53</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.868465382584397</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.928410638772357</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.141947917477947</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.347843704705012</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.09596201836242219</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1920827763584445</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.01201328929340104</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.169659667687212</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,19</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23,03</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-16,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-8,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-30,57%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.764233918306386</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.210592008719435</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.748847701853911</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.88444604532486</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2067174787123511</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2656572751022311</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.329562744775976</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4652507213961717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-24,72; 11,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,3; 40,65</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-35,49; 5,81</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-31,77; 19,91</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,88; 109,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-55,86; 10,63</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.781947341521233</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.463009119546453</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.826487050708612</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.485746836534141</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4732211764607296</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.8627501077966633</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4781528588091631</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2410499064708136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,74</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,38</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.209963299852105</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.843123144297448</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4.576800643306961</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.655708382594989</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2219959040888857</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1196425864059766</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.5591693177644506</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2695834183255565</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,95; 25,01</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-19,41; 22,51</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-14,87; 26,32</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-12,76; 46,65</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-29,14; 50,17</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-21,62; 57,53</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.69362392513274</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.72120864063622</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.4709129146132506</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-12.00894057547353</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4731456548498099</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4578062878814436</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.08189755570610928</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5752337924769342</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.238153148203539</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.60317461512035</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.42615286696926</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.998238005652932</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1114163191577366</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.3734964159689554</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.814590962406576</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.243320117376304</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-6.410446823237084</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.0956429848685908</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8467399280518886</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.8244994553455829</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3432147319021483</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.006763109630563197</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1010082564574913</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.07498855741241232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-12.31773750653079</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.562237875058766</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.512558836246239</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.747572458150887</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5659803050926185</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3251923114878624</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3559662008066248</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3575226692967868</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.06443144342451025</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.658168262030789</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.441678339393009</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.456356136959639</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.01381440887740116</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5152697918136629</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.9342664738480135</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.8212957361482731</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,98</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-8,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 14,36</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,41; 17,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-15,53; 5,23</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-6,48; 25,25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 33,29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-23,62; 9,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.514437309679839</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.7322723599786307</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.977215733059039</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.601321831781365</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.07604862347984856</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.05565355449221963</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2166425668212398</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1142263238015739</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.162714120891358</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.144569173446441</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.4410158789971705</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.628181376583795</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2338327333113071</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1511101729516584</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.05084802875635521</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2915416358481522</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.551920647295891</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.855364185873528</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.674636737829599</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.696051921258303</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08308181202454276</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.32375618310732</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.592219890013166</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1435783790311292</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
